--- a/calificaciones/P00-S02-corte-05sep.xlsx
+++ b/calificaciones/P00-S02-corte-05sep.xlsx
@@ -559,6 +559,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1027,7 +1028,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>tu prueba va en p00/prueba.txt (no en s02/) · usa tu rama entregas_guerrero_uriel · falta el contenido Docker del s02</t>
+          <t>tu prueba va en p00/prueba.txt (no en s02/) · usa tu rama entregas_apellido_nombre · falta el contenido Docker del s02</t>
         </is>
       </c>
     </row>
@@ -2041,6 +2042,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
@@ -2081,6 +2083,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2177,6 +2180,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
